--- a/sampling.info.xlsx
+++ b/sampling.info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devonderaad/Desktop/myzomela.rad/myzo.rad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6193C0F3-8657-7742-B1F6-DDC01273A379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FF79FD-6507-B24D-AC2C-FA3FEF774963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="820" windowWidth="17540" windowHeight="17920" xr2:uid="{DDB4E7F5-CD0E-3C4D-9B95-26D25AA36201}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="28920" windowHeight="17920" xr2:uid="{DDB4E7F5-CD0E-3C4D-9B95-26D25AA36201}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="275">
   <si>
     <t>Catalog</t>
   </si>
@@ -704,25 +704,10 @@
     <t>unknown</t>
   </si>
   <si>
-    <t>ANWC 54454</t>
-  </si>
-  <si>
     <t>erythrocephala</t>
   </si>
   <si>
     <t>Australia</t>
-  </si>
-  <si>
-    <t>ANWC 54455</t>
-  </si>
-  <si>
-    <t>ANWC 54483</t>
-  </si>
-  <si>
-    <t>ANWC 54585</t>
-  </si>
-  <si>
-    <t>ANWC 54617</t>
   </si>
   <si>
     <t>SKEL 30322</t>
@@ -882,7 +867,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -936,12 +921,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF4E565F"/>
       <name val="Helvetica Neue"/>
@@ -968,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -982,9 +961,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1319,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80F2D5D-AB1C-254C-AD27-DAA5C3473E3A}">
-  <dimension ref="A1:AU136"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
@@ -1389,13 +1367,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J2" s="6">
         <v>39421</v>
@@ -1427,13 +1405,13 @@
         <v>12</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J3" s="6">
         <v>39422</v>
@@ -1465,13 +1443,13 @@
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J4" s="6">
         <v>39741</v>
@@ -1503,13 +1481,13 @@
         <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J5" s="6">
         <v>39742</v>
@@ -1541,7 +1519,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>10</v>
@@ -1579,7 +1557,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>10</v>
@@ -1617,7 +1595,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>10</v>
@@ -1655,7 +1633,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>10</v>
@@ -1693,7 +1671,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>10</v>
@@ -1731,7 +1709,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>10</v>
@@ -1766,7 +1744,7 @@
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>38</v>
@@ -1801,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>38</v>
@@ -1836,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>38</v>
@@ -1871,7 +1849,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>38</v>
@@ -1906,7 +1884,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>38</v>
@@ -1924,12 +1902,12 @@
         <v>161.7315275</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>161</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
@@ -1944,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>38</v>
@@ -1961,15 +1939,13 @@
       <c r="L17">
         <v>161.7315275</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>162</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -1984,7 +1960,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>38</v>
@@ -2002,12 +1978,12 @@
         <v>161.7315275</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
@@ -2022,7 +1998,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>38</v>
@@ -2040,12 +2016,12 @@
         <v>161.7315275</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>44</v>
@@ -2060,7 +2036,7 @@
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>45</v>
@@ -2077,15 +2053,13 @@
       <c r="L20">
         <v>168.28270000000001</v>
       </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>47</v>
@@ -2100,7 +2074,7 @@
         <v>12</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>45</v>
@@ -2118,12 +2092,12 @@
         <v>167.43559999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>49</v>
@@ -2138,7 +2112,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>45</v>
@@ -2156,7 +2130,7 @@
         <v>167.43559999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>167</v>
       </c>
@@ -2173,7 +2147,7 @@
         <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>45</v>
@@ -2191,12 +2165,12 @@
         <v>167.5488</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>168</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>52</v>
@@ -2211,7 +2185,7 @@
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>45</v>
@@ -2229,12 +2203,12 @@
         <v>167.5488</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>169</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>53</v>
@@ -2249,7 +2223,7 @@
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>45</v>
@@ -2267,12 +2241,12 @@
         <v>167.52869999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>170</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>55</v>
@@ -2287,7 +2261,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>45</v>
@@ -2305,12 +2279,12 @@
         <v>168.28270000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>171</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>56</v>
@@ -2325,7 +2299,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>45</v>
@@ -2343,7 +2317,7 @@
         <v>167.5488</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -2360,7 +2334,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>45</v>
@@ -2378,12 +2352,12 @@
         <v>167.52869999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>173</v>
       </c>
       <c r="B29" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>58</v>
@@ -2398,7 +2372,7 @@
         <v>12</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>45</v>
@@ -2416,7 +2390,7 @@
         <v>168.28270000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -2433,7 +2407,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>45</v>
@@ -2451,12 +2425,12 @@
         <v>168.28270000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>60</v>
@@ -2471,7 +2445,7 @@
         <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>45</v>
@@ -2489,12 +2463,12 @@
         <v>167.43559999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>176</v>
       </c>
       <c r="B32" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>61</v>
@@ -2509,7 +2483,7 @@
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>45</v>
@@ -2532,7 +2506,7 @@
         <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>62</v>
@@ -2547,7 +2521,7 @@
         <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>45</v>
@@ -2570,7 +2544,7 @@
         <v>178</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>63</v>
@@ -2585,7 +2559,7 @@
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>45</v>
@@ -2623,7 +2597,7 @@
         <v>21</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>10</v>
@@ -2661,7 +2635,7 @@
         <v>21</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>10</v>
@@ -2699,7 +2673,7 @@
         <v>21</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>10</v>
@@ -2737,7 +2711,7 @@
         <v>21</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>10</v>
@@ -2775,7 +2749,7 @@
         <v>21</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>10</v>
@@ -2813,7 +2787,7 @@
         <v>21</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>10</v>
@@ -2851,13 +2825,13 @@
         <v>21</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J41" s="6">
         <v>42915</v>
@@ -2889,13 +2863,13 @@
         <v>21</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J42" s="6">
         <v>42917</v>
@@ -2927,13 +2901,13 @@
         <v>21</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J43" s="6">
         <v>42917</v>
@@ -2965,13 +2939,13 @@
         <v>21</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J44" s="6">
         <v>42918</v>
@@ -3003,13 +2977,13 @@
         <v>21</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J45" s="6">
         <v>42919</v>
@@ -3041,13 +3015,13 @@
         <v>21</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J46" s="6">
         <v>42920</v>
@@ -3085,7 +3059,7 @@
         <v>10</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J47" s="6">
         <v>42925</v>
@@ -3123,7 +3097,7 @@
         <v>10</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J48" s="6">
         <v>42929</v>
@@ -3541,13 +3515,13 @@
       <c r="I59" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="11">
         <v>37795</v>
       </c>
-      <c r="K59" s="13">
+      <c r="K59" s="12">
         <v>-8.7240000000000002</v>
       </c>
-      <c r="L59" s="13">
+      <c r="L59" s="12">
         <v>157.44399999999999</v>
       </c>
     </row>
@@ -3579,13 +3553,13 @@
       <c r="I60" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J60" s="12">
+      <c r="J60" s="11">
         <v>37795</v>
       </c>
-      <c r="K60" s="13">
+      <c r="K60" s="12">
         <v>-8.7240000000000002</v>
       </c>
-      <c r="L60" s="13">
+      <c r="L60" s="12">
         <v>157.44399999999999</v>
       </c>
     </row>
@@ -3741,7 +3715,7 @@
         <v>178.1083333</v>
       </c>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>188</v>
       </c>
@@ -3779,7 +3753,7 @@
         <v>179.21166669999999</v>
       </c>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>189</v>
       </c>
@@ -3817,7 +3791,7 @@
         <v>179.76166670000001</v>
       </c>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>193</v>
       </c>
@@ -3855,7 +3829,7 @@
         <v>178.93600000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>187</v>
       </c>
@@ -3893,7 +3867,7 @@
         <v>179.21166669999999</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>191</v>
       </c>
@@ -3931,7 +3905,7 @@
         <v>-178.24225129999999</v>
       </c>
     </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>186</v>
       </c>
@@ -3969,7 +3943,7 @@
         <v>178.4603333</v>
       </c>
     </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>117</v>
       </c>
@@ -3995,7 +3969,7 @@
         <v>10</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J71" s="6">
         <v>41931</v>
@@ -4007,7 +3981,7 @@
         <v>157.012</v>
       </c>
     </row>
-    <row r="72" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -4033,7 +4007,7 @@
         <v>10</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J72" s="6">
         <v>41933</v>
@@ -4045,7 +4019,7 @@
         <v>157.012</v>
       </c>
     </row>
-    <row r="73" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>119</v>
       </c>
@@ -4071,7 +4045,7 @@
         <v>10</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J73" s="6">
         <v>41938</v>
@@ -4083,7 +4057,7 @@
         <v>156.77799999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>120</v>
       </c>
@@ -4109,7 +4083,7 @@
         <v>10</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J74" s="6">
         <v>41938</v>
@@ -4121,7 +4095,7 @@
         <v>156.77799999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>121</v>
       </c>
@@ -4147,7 +4121,7 @@
         <v>10</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J75" s="6">
         <v>41941</v>
@@ -4159,7 +4133,7 @@
         <v>156.77799999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>122</v>
       </c>
@@ -4185,7 +4159,7 @@
         <v>10</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J76" s="6">
         <v>41948</v>
@@ -4197,7 +4171,7 @@
         <v>155.84700000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>123</v>
       </c>
@@ -4223,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J77" s="6">
         <v>41952</v>
@@ -4234,43 +4208,8 @@
       <c r="L77" s="2">
         <v>155.858</v>
       </c>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="2"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
-      <c r="Z77" s="2"/>
-      <c r="AA77" s="2"/>
-      <c r="AB77" s="2"/>
-      <c r="AC77" s="2"/>
-      <c r="AD77" s="2"/>
-      <c r="AE77" s="2"/>
-      <c r="AF77" s="2"/>
-      <c r="AG77" s="2"/>
-      <c r="AH77" s="2"/>
-      <c r="AI77" s="2"/>
-      <c r="AJ77" s="2"/>
-      <c r="AK77" s="2"/>
-      <c r="AL77" s="2"/>
-      <c r="AM77" s="2"/>
-      <c r="AN77" s="2"/>
-      <c r="AO77" s="2"/>
-      <c r="AP77" s="2"/>
-      <c r="AQ77" s="2"/>
-      <c r="AR77" s="2"/>
-      <c r="AS77" s="2"/>
-      <c r="AT77" s="2"/>
-      <c r="AU77" s="2"/>
-    </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>124</v>
       </c>
@@ -4307,43 +4246,8 @@
       <c r="L78" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
-      <c r="AA78" s="2"/>
-      <c r="AB78" s="2"/>
-      <c r="AC78" s="2"/>
-      <c r="AD78" s="2"/>
-      <c r="AE78" s="2"/>
-      <c r="AF78" s="2"/>
-      <c r="AG78" s="2"/>
-      <c r="AH78" s="2"/>
-      <c r="AI78" s="2"/>
-      <c r="AJ78" s="2"/>
-      <c r="AK78" s="2"/>
-      <c r="AL78" s="2"/>
-      <c r="AM78" s="2"/>
-      <c r="AN78" s="2"/>
-      <c r="AO78" s="2"/>
-      <c r="AP78" s="2"/>
-      <c r="AQ78" s="2"/>
-      <c r="AR78" s="2"/>
-      <c r="AS78" s="2"/>
-      <c r="AT78" s="2"/>
-      <c r="AU78" s="2"/>
-    </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>125</v>
       </c>
@@ -4380,43 +4284,8 @@
       <c r="L79" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
-      <c r="Y79" s="2"/>
-      <c r="Z79" s="2"/>
-      <c r="AA79" s="2"/>
-      <c r="AB79" s="2"/>
-      <c r="AC79" s="2"/>
-      <c r="AD79" s="2"/>
-      <c r="AE79" s="2"/>
-      <c r="AF79" s="2"/>
-      <c r="AG79" s="2"/>
-      <c r="AH79" s="2"/>
-      <c r="AI79" s="2"/>
-      <c r="AJ79" s="2"/>
-      <c r="AK79" s="2"/>
-      <c r="AL79" s="2"/>
-      <c r="AM79" s="2"/>
-      <c r="AN79" s="2"/>
-      <c r="AO79" s="2"/>
-      <c r="AP79" s="2"/>
-      <c r="AQ79" s="2"/>
-      <c r="AR79" s="2"/>
-      <c r="AS79" s="2"/>
-      <c r="AT79" s="2"/>
-      <c r="AU79" s="2"/>
-    </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>126</v>
       </c>
@@ -4453,43 +4322,8 @@
       <c r="L80" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="2"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
-      <c r="Y80" s="2"/>
-      <c r="Z80" s="2"/>
-      <c r="AA80" s="2"/>
-      <c r="AB80" s="2"/>
-      <c r="AC80" s="2"/>
-      <c r="AD80" s="2"/>
-      <c r="AE80" s="2"/>
-      <c r="AF80" s="2"/>
-      <c r="AG80" s="2"/>
-      <c r="AH80" s="2"/>
-      <c r="AI80" s="2"/>
-      <c r="AJ80" s="2"/>
-      <c r="AK80" s="2"/>
-      <c r="AL80" s="2"/>
-      <c r="AM80" s="2"/>
-      <c r="AN80" s="2"/>
-      <c r="AO80" s="2"/>
-      <c r="AP80" s="2"/>
-      <c r="AQ80" s="2"/>
-      <c r="AR80" s="2"/>
-      <c r="AS80" s="2"/>
-      <c r="AT80" s="2"/>
-      <c r="AU80" s="2"/>
-    </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>127</v>
       </c>
@@ -4526,43 +4360,8 @@
       <c r="L81" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
-      <c r="T81" s="2"/>
-      <c r="U81" s="2"/>
-      <c r="V81" s="2"/>
-      <c r="W81" s="2"/>
-      <c r="X81" s="2"/>
-      <c r="Y81" s="2"/>
-      <c r="Z81" s="2"/>
-      <c r="AA81" s="2"/>
-      <c r="AB81" s="2"/>
-      <c r="AC81" s="2"/>
-      <c r="AD81" s="2"/>
-      <c r="AE81" s="2"/>
-      <c r="AF81" s="2"/>
-      <c r="AG81" s="2"/>
-      <c r="AH81" s="2"/>
-      <c r="AI81" s="2"/>
-      <c r="AJ81" s="2"/>
-      <c r="AK81" s="2"/>
-      <c r="AL81" s="2"/>
-      <c r="AM81" s="2"/>
-      <c r="AN81" s="2"/>
-      <c r="AO81" s="2"/>
-      <c r="AP81" s="2"/>
-      <c r="AQ81" s="2"/>
-      <c r="AR81" s="2"/>
-      <c r="AS81" s="2"/>
-      <c r="AT81" s="2"/>
-      <c r="AU81" s="2"/>
-    </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>128</v>
       </c>
@@ -4599,43 +4398,8 @@
       <c r="L82" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="2"/>
-      <c r="U82" s="2"/>
-      <c r="V82" s="2"/>
-      <c r="W82" s="2"/>
-      <c r="X82" s="2"/>
-      <c r="Y82" s="2"/>
-      <c r="Z82" s="2"/>
-      <c r="AA82" s="2"/>
-      <c r="AB82" s="2"/>
-      <c r="AC82" s="2"/>
-      <c r="AD82" s="2"/>
-      <c r="AE82" s="2"/>
-      <c r="AF82" s="2"/>
-      <c r="AG82" s="2"/>
-      <c r="AH82" s="2"/>
-      <c r="AI82" s="2"/>
-      <c r="AJ82" s="2"/>
-      <c r="AK82" s="2"/>
-      <c r="AL82" s="2"/>
-      <c r="AM82" s="2"/>
-      <c r="AN82" s="2"/>
-      <c r="AO82" s="2"/>
-      <c r="AP82" s="2"/>
-      <c r="AQ82" s="2"/>
-      <c r="AR82" s="2"/>
-      <c r="AS82" s="2"/>
-      <c r="AT82" s="2"/>
-      <c r="AU82" s="2"/>
-    </row>
-    <row r="83" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>129</v>
       </c>
@@ -4661,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>221</v>
@@ -4672,43 +4436,8 @@
       <c r="L83" s="2">
         <v>159.54599999999999</v>
       </c>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
-      <c r="R83" s="2"/>
-      <c r="S83" s="2"/>
-      <c r="T83" s="2"/>
-      <c r="U83" s="2"/>
-      <c r="V83" s="2"/>
-      <c r="W83" s="2"/>
-      <c r="X83" s="2"/>
-      <c r="Y83" s="2"/>
-      <c r="Z83" s="2"/>
-      <c r="AA83" s="2"/>
-      <c r="AB83" s="2"/>
-      <c r="AC83" s="2"/>
-      <c r="AD83" s="2"/>
-      <c r="AE83" s="2"/>
-      <c r="AF83" s="2"/>
-      <c r="AG83" s="2"/>
-      <c r="AH83" s="2"/>
-      <c r="AI83" s="2"/>
-      <c r="AJ83" s="2"/>
-      <c r="AK83" s="2"/>
-      <c r="AL83" s="2"/>
-      <c r="AM83" s="2"/>
-      <c r="AN83" s="2"/>
-      <c r="AO83" s="2"/>
-      <c r="AP83" s="2"/>
-      <c r="AQ83" s="2"/>
-      <c r="AR83" s="2"/>
-      <c r="AS83" s="2"/>
-      <c r="AT83" s="2"/>
-      <c r="AU83" s="2"/>
-    </row>
-    <row r="84" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>130</v>
       </c>
@@ -4734,7 +4463,7 @@
         <v>10</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J84" s="6">
         <v>42163</v>
@@ -4745,43 +4474,8 @@
       <c r="L84" s="2">
         <v>160.989</v>
       </c>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
-      <c r="Q84" s="2"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
-      <c r="T84" s="2"/>
-      <c r="U84" s="2"/>
-      <c r="V84" s="2"/>
-      <c r="W84" s="2"/>
-      <c r="X84" s="2"/>
-      <c r="Y84" s="2"/>
-      <c r="Z84" s="2"/>
-      <c r="AA84" s="2"/>
-      <c r="AB84" s="2"/>
-      <c r="AC84" s="2"/>
-      <c r="AD84" s="2"/>
-      <c r="AE84" s="2"/>
-      <c r="AF84" s="2"/>
-      <c r="AG84" s="2"/>
-      <c r="AH84" s="2"/>
-      <c r="AI84" s="2"/>
-      <c r="AJ84" s="2"/>
-      <c r="AK84" s="2"/>
-      <c r="AL84" s="2"/>
-      <c r="AM84" s="2"/>
-      <c r="AN84" s="2"/>
-      <c r="AO84" s="2"/>
-      <c r="AP84" s="2"/>
-      <c r="AQ84" s="2"/>
-      <c r="AR84" s="2"/>
-      <c r="AS84" s="2"/>
-      <c r="AT84" s="2"/>
-      <c r="AU84" s="2"/>
-    </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>131</v>
       </c>
@@ -4807,7 +4501,7 @@
         <v>10</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J85" s="6">
         <v>42167</v>
@@ -4818,43 +4512,8 @@
       <c r="L85" s="2">
         <v>160.989</v>
       </c>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="2"/>
-      <c r="W85" s="2"/>
-      <c r="X85" s="2"/>
-      <c r="Y85" s="2"/>
-      <c r="Z85" s="2"/>
-      <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
-      <c r="AC85" s="2"/>
-      <c r="AD85" s="2"/>
-      <c r="AE85" s="2"/>
-      <c r="AF85" s="2"/>
-      <c r="AG85" s="2"/>
-      <c r="AH85" s="2"/>
-      <c r="AI85" s="2"/>
-      <c r="AJ85" s="2"/>
-      <c r="AK85" s="2"/>
-      <c r="AL85" s="2"/>
-      <c r="AM85" s="2"/>
-      <c r="AN85" s="2"/>
-      <c r="AO85" s="2"/>
-      <c r="AP85" s="2"/>
-      <c r="AQ85" s="2"/>
-      <c r="AR85" s="2"/>
-      <c r="AS85" s="2"/>
-      <c r="AT85" s="2"/>
-      <c r="AU85" s="2"/>
-    </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>132</v>
       </c>
@@ -4880,7 +4539,7 @@
         <v>10</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J86" s="6">
         <v>42172</v>
@@ -4891,43 +4550,8 @@
       <c r="L86" s="2">
         <v>161.12799999999999</v>
       </c>
-      <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
-      <c r="T86" s="2"/>
-      <c r="U86" s="2"/>
-      <c r="V86" s="2"/>
-      <c r="W86" s="2"/>
-      <c r="X86" s="2"/>
-      <c r="Y86" s="2"/>
-      <c r="Z86" s="2"/>
-      <c r="AA86" s="2"/>
-      <c r="AB86" s="2"/>
-      <c r="AC86" s="2"/>
-      <c r="AD86" s="2"/>
-      <c r="AE86" s="2"/>
-      <c r="AF86" s="2"/>
-      <c r="AG86" s="2"/>
-      <c r="AH86" s="2"/>
-      <c r="AI86" s="2"/>
-      <c r="AJ86" s="2"/>
-      <c r="AK86" s="2"/>
-      <c r="AL86" s="2"/>
-      <c r="AM86" s="2"/>
-      <c r="AN86" s="2"/>
-      <c r="AO86" s="2"/>
-      <c r="AP86" s="2"/>
-      <c r="AQ86" s="2"/>
-      <c r="AR86" s="2"/>
-      <c r="AS86" s="2"/>
-      <c r="AT86" s="2"/>
-      <c r="AU86" s="2"/>
-    </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>133</v>
       </c>
@@ -4953,7 +4577,7 @@
         <v>10</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J87" s="6">
         <v>42180</v>
@@ -4964,43 +4588,8 @@
       <c r="L87" s="2">
         <v>160.86799999999999</v>
       </c>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
-      <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="2"/>
-      <c r="AB87" s="2"/>
-      <c r="AC87" s="2"/>
-      <c r="AD87" s="2"/>
-      <c r="AE87" s="2"/>
-      <c r="AF87" s="2"/>
-      <c r="AG87" s="2"/>
-      <c r="AH87" s="2"/>
-      <c r="AI87" s="2"/>
-      <c r="AJ87" s="2"/>
-      <c r="AK87" s="2"/>
-      <c r="AL87" s="2"/>
-      <c r="AM87" s="2"/>
-      <c r="AN87" s="2"/>
-      <c r="AO87" s="2"/>
-      <c r="AP87" s="2"/>
-      <c r="AQ87" s="2"/>
-      <c r="AR87" s="2"/>
-      <c r="AS87" s="2"/>
-      <c r="AT87" s="2"/>
-      <c r="AU87" s="2"/>
-    </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>134</v>
       </c>
@@ -5026,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J88" s="6">
         <v>42181</v>
@@ -5037,43 +4626,8 @@
       <c r="L88" s="2">
         <v>160.86799999999999</v>
       </c>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
-      <c r="Y88" s="2"/>
-      <c r="Z88" s="2"/>
-      <c r="AA88" s="2"/>
-      <c r="AB88" s="2"/>
-      <c r="AC88" s="2"/>
-      <c r="AD88" s="2"/>
-      <c r="AE88" s="2"/>
-      <c r="AF88" s="2"/>
-      <c r="AG88" s="2"/>
-      <c r="AH88" s="2"/>
-      <c r="AI88" s="2"/>
-      <c r="AJ88" s="2"/>
-      <c r="AK88" s="2"/>
-      <c r="AL88" s="2"/>
-      <c r="AM88" s="2"/>
-      <c r="AN88" s="2"/>
-      <c r="AO88" s="2"/>
-      <c r="AP88" s="2"/>
-      <c r="AQ88" s="2"/>
-      <c r="AR88" s="2"/>
-      <c r="AS88" s="2"/>
-      <c r="AT88" s="2"/>
-      <c r="AU88" s="2"/>
-    </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>135</v>
       </c>
@@ -5099,7 +4653,7 @@
         <v>10</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>221</v>
@@ -5110,43 +4664,8 @@
       <c r="L89" s="2">
         <v>160.86799999999999</v>
       </c>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="2"/>
-      <c r="W89" s="2"/>
-      <c r="X89" s="2"/>
-      <c r="Y89" s="2"/>
-      <c r="Z89" s="2"/>
-      <c r="AA89" s="2"/>
-      <c r="AB89" s="2"/>
-      <c r="AC89" s="2"/>
-      <c r="AD89" s="2"/>
-      <c r="AE89" s="2"/>
-      <c r="AF89" s="2"/>
-      <c r="AG89" s="2"/>
-      <c r="AH89" s="2"/>
-      <c r="AI89" s="2"/>
-      <c r="AJ89" s="2"/>
-      <c r="AK89" s="2"/>
-      <c r="AL89" s="2"/>
-      <c r="AM89" s="2"/>
-      <c r="AN89" s="2"/>
-      <c r="AO89" s="2"/>
-      <c r="AP89" s="2"/>
-      <c r="AQ89" s="2"/>
-      <c r="AR89" s="2"/>
-      <c r="AS89" s="2"/>
-      <c r="AT89" s="2"/>
-      <c r="AU89" s="2"/>
-    </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>136</v>
       </c>
@@ -5172,7 +4691,7 @@
         <v>10</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J90" s="6">
         <v>39410</v>
@@ -5183,43 +4702,8 @@
       <c r="L90" s="2">
         <v>159.97999999999999</v>
       </c>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
-      <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
-      <c r="V90" s="2"/>
-      <c r="W90" s="2"/>
-      <c r="X90" s="2"/>
-      <c r="Y90" s="2"/>
-      <c r="Z90" s="2"/>
-      <c r="AA90" s="2"/>
-      <c r="AB90" s="2"/>
-      <c r="AC90" s="2"/>
-      <c r="AD90" s="2"/>
-      <c r="AE90" s="2"/>
-      <c r="AF90" s="2"/>
-      <c r="AG90" s="2"/>
-      <c r="AH90" s="2"/>
-      <c r="AI90" s="2"/>
-      <c r="AJ90" s="2"/>
-      <c r="AK90" s="2"/>
-      <c r="AL90" s="2"/>
-      <c r="AM90" s="2"/>
-      <c r="AN90" s="2"/>
-      <c r="AO90" s="2"/>
-      <c r="AP90" s="2"/>
-      <c r="AQ90" s="2"/>
-      <c r="AR90" s="2"/>
-      <c r="AS90" s="2"/>
-      <c r="AT90" s="2"/>
-      <c r="AU90" s="2"/>
-    </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>137</v>
       </c>
@@ -5245,7 +4729,7 @@
         <v>10</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J91" s="6">
         <v>39414</v>
@@ -5256,43 +4740,8 @@
       <c r="L91" s="2">
         <v>159.97999999999999</v>
       </c>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
-      <c r="T91" s="2"/>
-      <c r="U91" s="2"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="2"/>
-      <c r="X91" s="2"/>
-      <c r="Y91" s="2"/>
-      <c r="Z91" s="2"/>
-      <c r="AA91" s="2"/>
-      <c r="AB91" s="2"/>
-      <c r="AC91" s="2"/>
-      <c r="AD91" s="2"/>
-      <c r="AE91" s="2"/>
-      <c r="AF91" s="2"/>
-      <c r="AG91" s="2"/>
-      <c r="AH91" s="2"/>
-      <c r="AI91" s="2"/>
-      <c r="AJ91" s="2"/>
-      <c r="AK91" s="2"/>
-      <c r="AL91" s="2"/>
-      <c r="AM91" s="2"/>
-      <c r="AN91" s="2"/>
-      <c r="AO91" s="2"/>
-      <c r="AP91" s="2"/>
-      <c r="AQ91" s="2"/>
-      <c r="AR91" s="2"/>
-      <c r="AS91" s="2"/>
-      <c r="AT91" s="2"/>
-      <c r="AU91" s="2"/>
-    </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>138</v>
       </c>
@@ -5329,43 +4778,8 @@
       <c r="L92" s="2">
         <v>160.05850000000001</v>
       </c>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
-      <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="2"/>
-      <c r="X92" s="2"/>
-      <c r="Y92" s="2"/>
-      <c r="Z92" s="2"/>
-      <c r="AA92" s="2"/>
-      <c r="AB92" s="2"/>
-      <c r="AC92" s="2"/>
-      <c r="AD92" s="2"/>
-      <c r="AE92" s="2"/>
-      <c r="AF92" s="2"/>
-      <c r="AG92" s="2"/>
-      <c r="AH92" s="2"/>
-      <c r="AI92" s="2"/>
-      <c r="AJ92" s="2"/>
-      <c r="AK92" s="2"/>
-      <c r="AL92" s="2"/>
-      <c r="AM92" s="2"/>
-      <c r="AN92" s="2"/>
-      <c r="AO92" s="2"/>
-      <c r="AP92" s="2"/>
-      <c r="AQ92" s="2"/>
-      <c r="AR92" s="2"/>
-      <c r="AS92" s="2"/>
-      <c r="AT92" s="2"/>
-      <c r="AU92" s="2"/>
-    </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>139</v>
       </c>
@@ -5402,43 +4816,8 @@
       <c r="L93" s="2">
         <v>160.05850000000001</v>
       </c>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-      <c r="T93" s="2"/>
-      <c r="U93" s="2"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
-      <c r="X93" s="2"/>
-      <c r="Y93" s="2"/>
-      <c r="Z93" s="2"/>
-      <c r="AA93" s="2"/>
-      <c r="AB93" s="2"/>
-      <c r="AC93" s="2"/>
-      <c r="AD93" s="2"/>
-      <c r="AE93" s="2"/>
-      <c r="AF93" s="2"/>
-      <c r="AG93" s="2"/>
-      <c r="AH93" s="2"/>
-      <c r="AI93" s="2"/>
-      <c r="AJ93" s="2"/>
-      <c r="AK93" s="2"/>
-      <c r="AL93" s="2"/>
-      <c r="AM93" s="2"/>
-      <c r="AN93" s="2"/>
-      <c r="AO93" s="2"/>
-      <c r="AP93" s="2"/>
-      <c r="AQ93" s="2"/>
-      <c r="AR93" s="2"/>
-      <c r="AS93" s="2"/>
-      <c r="AT93" s="2"/>
-      <c r="AU93" s="2"/>
-    </row>
-    <row r="94" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>140</v>
       </c>
@@ -5475,43 +4854,8 @@
       <c r="L94" s="2">
         <v>160.05850000000001</v>
       </c>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
-      <c r="Q94" s="2"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
-      <c r="T94" s="2"/>
-      <c r="U94" s="2"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="2"/>
-      <c r="X94" s="2"/>
-      <c r="Y94" s="2"/>
-      <c r="Z94" s="2"/>
-      <c r="AA94" s="2"/>
-      <c r="AB94" s="2"/>
-      <c r="AC94" s="2"/>
-      <c r="AD94" s="2"/>
-      <c r="AE94" s="2"/>
-      <c r="AF94" s="2"/>
-      <c r="AG94" s="2"/>
-      <c r="AH94" s="2"/>
-      <c r="AI94" s="2"/>
-      <c r="AJ94" s="2"/>
-      <c r="AK94" s="2"/>
-      <c r="AL94" s="2"/>
-      <c r="AM94" s="2"/>
-      <c r="AN94" s="2"/>
-      <c r="AO94" s="2"/>
-      <c r="AP94" s="2"/>
-      <c r="AQ94" s="2"/>
-      <c r="AR94" s="2"/>
-      <c r="AS94" s="2"/>
-      <c r="AT94" s="2"/>
-      <c r="AU94" s="2"/>
-    </row>
-    <row r="95" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>141</v>
       </c>
@@ -5548,43 +4892,8 @@
       <c r="L95" s="2">
         <v>160.05850000000001</v>
       </c>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
-      <c r="Q95" s="2"/>
-      <c r="R95" s="2"/>
-      <c r="S95" s="2"/>
-      <c r="T95" s="2"/>
-      <c r="U95" s="2"/>
-      <c r="V95" s="2"/>
-      <c r="W95" s="2"/>
-      <c r="X95" s="2"/>
-      <c r="Y95" s="2"/>
-      <c r="Z95" s="2"/>
-      <c r="AA95" s="2"/>
-      <c r="AB95" s="2"/>
-      <c r="AC95" s="2"/>
-      <c r="AD95" s="2"/>
-      <c r="AE95" s="2"/>
-      <c r="AF95" s="2"/>
-      <c r="AG95" s="2"/>
-      <c r="AH95" s="2"/>
-      <c r="AI95" s="2"/>
-      <c r="AJ95" s="2"/>
-      <c r="AK95" s="2"/>
-      <c r="AL95" s="2"/>
-      <c r="AM95" s="2"/>
-      <c r="AN95" s="2"/>
-      <c r="AO95" s="2"/>
-      <c r="AP95" s="2"/>
-      <c r="AQ95" s="2"/>
-      <c r="AR95" s="2"/>
-      <c r="AS95" s="2"/>
-      <c r="AT95" s="2"/>
-      <c r="AU95" s="2"/>
-    </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>195</v>
       </c>
@@ -5604,7 +4913,7 @@
         <v>70</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>71</v>
@@ -5621,43 +4930,8 @@
       <c r="L96" s="2">
         <v>150.67781669999999</v>
       </c>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" s="2"/>
-      <c r="Q96" s="2"/>
-      <c r="R96" s="2"/>
-      <c r="S96" s="2"/>
-      <c r="T96" s="2"/>
-      <c r="U96" s="2"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="2"/>
-      <c r="X96" s="2"/>
-      <c r="Y96" s="2"/>
-      <c r="Z96" s="2"/>
-      <c r="AA96" s="2"/>
-      <c r="AB96" s="2"/>
-      <c r="AC96" s="2"/>
-      <c r="AD96" s="2"/>
-      <c r="AE96" s="2"/>
-      <c r="AF96" s="2"/>
-      <c r="AG96" s="2"/>
-      <c r="AH96" s="2"/>
-      <c r="AI96" s="2"/>
-      <c r="AJ96" s="2"/>
-      <c r="AK96" s="2"/>
-      <c r="AL96" s="2"/>
-      <c r="AM96" s="2"/>
-      <c r="AN96" s="2"/>
-      <c r="AO96" s="2"/>
-      <c r="AP96" s="2"/>
-      <c r="AQ96" s="2"/>
-      <c r="AR96" s="2"/>
-      <c r="AS96" s="2"/>
-      <c r="AT96" s="2"/>
-      <c r="AU96" s="2"/>
-    </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>196</v>
       </c>
@@ -5677,7 +4951,7 @@
         <v>70</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>71</v>
@@ -5694,43 +4968,8 @@
       <c r="L97" s="2">
         <v>150.67781669999999</v>
       </c>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" s="2"/>
-      <c r="Q97" s="2"/>
-      <c r="R97" s="2"/>
-      <c r="S97" s="2"/>
-      <c r="T97" s="2"/>
-      <c r="U97" s="2"/>
-      <c r="V97" s="2"/>
-      <c r="W97" s="2"/>
-      <c r="X97" s="2"/>
-      <c r="Y97" s="2"/>
-      <c r="Z97" s="2"/>
-      <c r="AA97" s="2"/>
-      <c r="AB97" s="2"/>
-      <c r="AC97" s="2"/>
-      <c r="AD97" s="2"/>
-      <c r="AE97" s="2"/>
-      <c r="AF97" s="2"/>
-      <c r="AG97" s="2"/>
-      <c r="AH97" s="2"/>
-      <c r="AI97" s="2"/>
-      <c r="AJ97" s="2"/>
-      <c r="AK97" s="2"/>
-      <c r="AL97" s="2"/>
-      <c r="AM97" s="2"/>
-      <c r="AN97" s="2"/>
-      <c r="AO97" s="2"/>
-      <c r="AP97" s="2"/>
-      <c r="AQ97" s="2"/>
-      <c r="AR97" s="2"/>
-      <c r="AS97" s="2"/>
-      <c r="AT97" s="2"/>
-      <c r="AU97" s="2"/>
-    </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -5750,7 +4989,7 @@
         <v>70</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>71</v>
@@ -5767,43 +5006,8 @@
       <c r="L98" s="2">
         <v>150.67781669999999</v>
       </c>
-      <c r="M98" s="2"/>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" s="2"/>
-      <c r="Q98" s="2"/>
-      <c r="R98" s="2"/>
-      <c r="S98" s="2"/>
-      <c r="T98" s="2"/>
-      <c r="U98" s="2"/>
-      <c r="V98" s="2"/>
-      <c r="W98" s="2"/>
-      <c r="X98" s="2"/>
-      <c r="Y98" s="2"/>
-      <c r="Z98" s="2"/>
-      <c r="AA98" s="2"/>
-      <c r="AB98" s="2"/>
-      <c r="AC98" s="2"/>
-      <c r="AD98" s="2"/>
-      <c r="AE98" s="2"/>
-      <c r="AF98" s="2"/>
-      <c r="AG98" s="2"/>
-      <c r="AH98" s="2"/>
-      <c r="AI98" s="2"/>
-      <c r="AJ98" s="2"/>
-      <c r="AK98" s="2"/>
-      <c r="AL98" s="2"/>
-      <c r="AM98" s="2"/>
-      <c r="AN98" s="2"/>
-      <c r="AO98" s="2"/>
-      <c r="AP98" s="2"/>
-      <c r="AQ98" s="2"/>
-      <c r="AR98" s="2"/>
-      <c r="AS98" s="2"/>
-      <c r="AT98" s="2"/>
-      <c r="AU98" s="2"/>
-    </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>142</v>
       </c>
@@ -5829,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>221</v>
@@ -5840,43 +5044,8 @@
       <c r="L99" s="2">
         <v>151.93045000000001</v>
       </c>
-      <c r="M99" s="2"/>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" s="2"/>
-      <c r="Q99" s="2"/>
-      <c r="R99" s="2"/>
-      <c r="S99" s="2"/>
-      <c r="T99" s="2"/>
-      <c r="U99" s="2"/>
-      <c r="V99" s="2"/>
-      <c r="W99" s="2"/>
-      <c r="X99" s="2"/>
-      <c r="Y99" s="2"/>
-      <c r="Z99" s="2"/>
-      <c r="AA99" s="2"/>
-      <c r="AB99" s="2"/>
-      <c r="AC99" s="2"/>
-      <c r="AD99" s="2"/>
-      <c r="AE99" s="2"/>
-      <c r="AF99" s="2"/>
-      <c r="AG99" s="2"/>
-      <c r="AH99" s="2"/>
-      <c r="AI99" s="2"/>
-      <c r="AJ99" s="2"/>
-      <c r="AK99" s="2"/>
-      <c r="AL99" s="2"/>
-      <c r="AM99" s="2"/>
-      <c r="AN99" s="2"/>
-      <c r="AO99" s="2"/>
-      <c r="AP99" s="2"/>
-      <c r="AQ99" s="2"/>
-      <c r="AR99" s="2"/>
-      <c r="AS99" s="2"/>
-      <c r="AT99" s="2"/>
-      <c r="AU99" s="2"/>
-    </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>143</v>
       </c>
@@ -5902,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>221</v>
@@ -5913,43 +5082,8 @@
       <c r="L100" s="2">
         <v>151.93045000000001</v>
       </c>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" s="2"/>
-      <c r="Q100" s="2"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-      <c r="T100" s="2"/>
-      <c r="U100" s="2"/>
-      <c r="V100" s="2"/>
-      <c r="W100" s="2"/>
-      <c r="X100" s="2"/>
-      <c r="Y100" s="2"/>
-      <c r="Z100" s="2"/>
-      <c r="AA100" s="2"/>
-      <c r="AB100" s="2"/>
-      <c r="AC100" s="2"/>
-      <c r="AD100" s="2"/>
-      <c r="AE100" s="2"/>
-      <c r="AF100" s="2"/>
-      <c r="AG100" s="2"/>
-      <c r="AH100" s="2"/>
-      <c r="AI100" s="2"/>
-      <c r="AJ100" s="2"/>
-      <c r="AK100" s="2"/>
-      <c r="AL100" s="2"/>
-      <c r="AM100" s="2"/>
-      <c r="AN100" s="2"/>
-      <c r="AO100" s="2"/>
-      <c r="AP100" s="2"/>
-      <c r="AQ100" s="2"/>
-      <c r="AR100" s="2"/>
-      <c r="AS100" s="2"/>
-      <c r="AT100" s="2"/>
-      <c r="AU100" s="2"/>
-    </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>144</v>
       </c>
@@ -5975,7 +5109,7 @@
         <v>15</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J101" s="6">
         <v>41203</v>
@@ -5986,43 +5120,8 @@
       <c r="L101" s="2">
         <v>151.93045000000001</v>
       </c>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" s="2"/>
-      <c r="Q101" s="2"/>
-      <c r="R101" s="2"/>
-      <c r="S101" s="2"/>
-      <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
-      <c r="V101" s="2"/>
-      <c r="W101" s="2"/>
-      <c r="X101" s="2"/>
-      <c r="Y101" s="2"/>
-      <c r="Z101" s="2"/>
-      <c r="AA101" s="2"/>
-      <c r="AB101" s="2"/>
-      <c r="AC101" s="2"/>
-      <c r="AD101" s="2"/>
-      <c r="AE101" s="2"/>
-      <c r="AF101" s="2"/>
-      <c r="AG101" s="2"/>
-      <c r="AH101" s="2"/>
-      <c r="AI101" s="2"/>
-      <c r="AJ101" s="2"/>
-      <c r="AK101" s="2"/>
-      <c r="AL101" s="2"/>
-      <c r="AM101" s="2"/>
-      <c r="AN101" s="2"/>
-      <c r="AO101" s="2"/>
-      <c r="AP101" s="2"/>
-      <c r="AQ101" s="2"/>
-      <c r="AR101" s="2"/>
-      <c r="AS101" s="2"/>
-      <c r="AT101" s="2"/>
-      <c r="AU101" s="2"/>
-    </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>145</v>
       </c>
@@ -6048,7 +5147,7 @@
         <v>15</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>221</v>
@@ -6059,43 +5158,8 @@
       <c r="L102" s="2">
         <v>151.93045000000001</v>
       </c>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" s="2"/>
-      <c r="Q102" s="2"/>
-      <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
-      <c r="T102" s="2"/>
-      <c r="U102" s="2"/>
-      <c r="V102" s="2"/>
-      <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-      <c r="Y102" s="2"/>
-      <c r="Z102" s="2"/>
-      <c r="AA102" s="2"/>
-      <c r="AB102" s="2"/>
-      <c r="AC102" s="2"/>
-      <c r="AD102" s="2"/>
-      <c r="AE102" s="2"/>
-      <c r="AF102" s="2"/>
-      <c r="AG102" s="2"/>
-      <c r="AH102" s="2"/>
-      <c r="AI102" s="2"/>
-      <c r="AJ102" s="2"/>
-      <c r="AK102" s="2"/>
-      <c r="AL102" s="2"/>
-      <c r="AM102" s="2"/>
-      <c r="AN102" s="2"/>
-      <c r="AO102" s="2"/>
-      <c r="AP102" s="2"/>
-      <c r="AQ102" s="2"/>
-      <c r="AR102" s="2"/>
-      <c r="AS102" s="2"/>
-      <c r="AT102" s="2"/>
-      <c r="AU102" s="2"/>
-    </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>146</v>
       </c>
@@ -6121,7 +5185,7 @@
         <v>15</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>221</v>
@@ -6132,43 +5196,8 @@
       <c r="L103" s="2">
         <v>151.93045000000001</v>
       </c>
-      <c r="M103" s="2"/>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" s="2"/>
-      <c r="Q103" s="2"/>
-      <c r="R103" s="2"/>
-      <c r="S103" s="2"/>
-      <c r="T103" s="2"/>
-      <c r="U103" s="2"/>
-      <c r="V103" s="2"/>
-      <c r="W103" s="2"/>
-      <c r="X103" s="2"/>
-      <c r="Y103" s="2"/>
-      <c r="Z103" s="2"/>
-      <c r="AA103" s="2"/>
-      <c r="AB103" s="2"/>
-      <c r="AC103" s="2"/>
-      <c r="AD103" s="2"/>
-      <c r="AE103" s="2"/>
-      <c r="AF103" s="2"/>
-      <c r="AG103" s="2"/>
-      <c r="AH103" s="2"/>
-      <c r="AI103" s="2"/>
-      <c r="AJ103" s="2"/>
-      <c r="AK103" s="2"/>
-      <c r="AL103" s="2"/>
-      <c r="AM103" s="2"/>
-      <c r="AN103" s="2"/>
-      <c r="AO103" s="2"/>
-      <c r="AP103" s="2"/>
-      <c r="AQ103" s="2"/>
-      <c r="AR103" s="2"/>
-      <c r="AS103" s="2"/>
-      <c r="AT103" s="2"/>
-      <c r="AU103" s="2"/>
-    </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -6188,7 +5217,7 @@
         <v>73</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>74</v>
@@ -6205,43 +5234,8 @@
       <c r="L104" s="2">
         <v>145.80600000000001</v>
       </c>
-      <c r="M104" s="2"/>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" s="2"/>
-      <c r="Q104" s="2"/>
-      <c r="R104" s="2"/>
-      <c r="S104" s="2"/>
-      <c r="T104" s="2"/>
-      <c r="U104" s="2"/>
-      <c r="V104" s="2"/>
-      <c r="W104" s="2"/>
-      <c r="X104" s="2"/>
-      <c r="Y104" s="2"/>
-      <c r="Z104" s="2"/>
-      <c r="AA104" s="2"/>
-      <c r="AB104" s="2"/>
-      <c r="AC104" s="2"/>
-      <c r="AD104" s="2"/>
-      <c r="AE104" s="2"/>
-      <c r="AF104" s="2"/>
-      <c r="AG104" s="2"/>
-      <c r="AH104" s="2"/>
-      <c r="AI104" s="2"/>
-      <c r="AJ104" s="2"/>
-      <c r="AK104" s="2"/>
-      <c r="AL104" s="2"/>
-      <c r="AM104" s="2"/>
-      <c r="AN104" s="2"/>
-      <c r="AO104" s="2"/>
-      <c r="AP104" s="2"/>
-      <c r="AQ104" s="2"/>
-      <c r="AR104" s="2"/>
-      <c r="AS104" s="2"/>
-      <c r="AT104" s="2"/>
-      <c r="AU104" s="2"/>
-    </row>
-    <row r="105" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>198</v>
       </c>
@@ -6261,7 +5255,7 @@
         <v>73</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>74</v>
@@ -6278,43 +5272,8 @@
       <c r="L105" s="2">
         <v>145.80600000000001</v>
       </c>
-      <c r="M105" s="2"/>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" s="2"/>
-      <c r="Q105" s="2"/>
-      <c r="R105" s="2"/>
-      <c r="S105" s="2"/>
-      <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
-      <c r="W105" s="2"/>
-      <c r="X105" s="2"/>
-      <c r="Y105" s="2"/>
-      <c r="Z105" s="2"/>
-      <c r="AA105" s="2"/>
-      <c r="AB105" s="2"/>
-      <c r="AC105" s="2"/>
-      <c r="AD105" s="2"/>
-      <c r="AE105" s="2"/>
-      <c r="AF105" s="2"/>
-      <c r="AG105" s="2"/>
-      <c r="AH105" s="2"/>
-      <c r="AI105" s="2"/>
-      <c r="AJ105" s="2"/>
-      <c r="AK105" s="2"/>
-      <c r="AL105" s="2"/>
-      <c r="AM105" s="2"/>
-      <c r="AN105" s="2"/>
-      <c r="AO105" s="2"/>
-      <c r="AP105" s="2"/>
-      <c r="AQ105" s="2"/>
-      <c r="AR105" s="2"/>
-      <c r="AS105" s="2"/>
-      <c r="AT105" s="2"/>
-      <c r="AU105" s="2"/>
-    </row>
-    <row r="106" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>199</v>
       </c>
@@ -6334,7 +5293,7 @@
         <v>73</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>74</v>
@@ -6351,43 +5310,8 @@
       <c r="L106" s="2">
         <v>145.80600000000001</v>
       </c>
-      <c r="M106" s="2"/>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" s="2"/>
-      <c r="Q106" s="2"/>
-      <c r="R106" s="2"/>
-      <c r="S106" s="2"/>
-      <c r="T106" s="2"/>
-      <c r="U106" s="2"/>
-      <c r="V106" s="2"/>
-      <c r="W106" s="2"/>
-      <c r="X106" s="2"/>
-      <c r="Y106" s="2"/>
-      <c r="Z106" s="2"/>
-      <c r="AA106" s="2"/>
-      <c r="AB106" s="2"/>
-      <c r="AC106" s="2"/>
-      <c r="AD106" s="2"/>
-      <c r="AE106" s="2"/>
-      <c r="AF106" s="2"/>
-      <c r="AG106" s="2"/>
-      <c r="AH106" s="2"/>
-      <c r="AI106" s="2"/>
-      <c r="AJ106" s="2"/>
-      <c r="AK106" s="2"/>
-      <c r="AL106" s="2"/>
-      <c r="AM106" s="2"/>
-      <c r="AN106" s="2"/>
-      <c r="AO106" s="2"/>
-      <c r="AP106" s="2"/>
-      <c r="AQ106" s="2"/>
-      <c r="AR106" s="2"/>
-      <c r="AS106" s="2"/>
-      <c r="AT106" s="2"/>
-      <c r="AU106" s="2"/>
-    </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>203</v>
       </c>
@@ -6407,7 +5331,7 @@
         <v>73</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>76</v>
@@ -6424,43 +5348,8 @@
       <c r="L107" s="2">
         <v>134.233</v>
       </c>
-      <c r="M107" s="2"/>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" s="2"/>
-      <c r="Q107" s="2"/>
-      <c r="R107" s="2"/>
-      <c r="S107" s="2"/>
-      <c r="T107" s="2"/>
-      <c r="U107" s="2"/>
-      <c r="V107" s="2"/>
-      <c r="W107" s="2"/>
-      <c r="X107" s="2"/>
-      <c r="Y107" s="2"/>
-      <c r="Z107" s="2"/>
-      <c r="AA107" s="2"/>
-      <c r="AB107" s="2"/>
-      <c r="AC107" s="2"/>
-      <c r="AD107" s="2"/>
-      <c r="AE107" s="2"/>
-      <c r="AF107" s="2"/>
-      <c r="AG107" s="2"/>
-      <c r="AH107" s="2"/>
-      <c r="AI107" s="2"/>
-      <c r="AJ107" s="2"/>
-      <c r="AK107" s="2"/>
-      <c r="AL107" s="2"/>
-      <c r="AM107" s="2"/>
-      <c r="AN107" s="2"/>
-      <c r="AO107" s="2"/>
-      <c r="AP107" s="2"/>
-      <c r="AQ107" s="2"/>
-      <c r="AR107" s="2"/>
-      <c r="AS107" s="2"/>
-      <c r="AT107" s="2"/>
-      <c r="AU107" s="2"/>
-    </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>200</v>
       </c>
@@ -6480,7 +5369,7 @@
         <v>73</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>76</v>
@@ -6497,43 +5386,8 @@
       <c r="L108" s="2">
         <v>134.64212000000001</v>
       </c>
-      <c r="M108" s="2"/>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" s="2"/>
-      <c r="Q108" s="2"/>
-      <c r="R108" s="2"/>
-      <c r="S108" s="2"/>
-      <c r="T108" s="2"/>
-      <c r="U108" s="2"/>
-      <c r="V108" s="2"/>
-      <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
-      <c r="Y108" s="2"/>
-      <c r="Z108" s="2"/>
-      <c r="AA108" s="2"/>
-      <c r="AB108" s="2"/>
-      <c r="AC108" s="2"/>
-      <c r="AD108" s="2"/>
-      <c r="AE108" s="2"/>
-      <c r="AF108" s="2"/>
-      <c r="AG108" s="2"/>
-      <c r="AH108" s="2"/>
-      <c r="AI108" s="2"/>
-      <c r="AJ108" s="2"/>
-      <c r="AK108" s="2"/>
-      <c r="AL108" s="2"/>
-      <c r="AM108" s="2"/>
-      <c r="AN108" s="2"/>
-      <c r="AO108" s="2"/>
-      <c r="AP108" s="2"/>
-      <c r="AQ108" s="2"/>
-      <c r="AR108" s="2"/>
-      <c r="AS108" s="2"/>
-      <c r="AT108" s="2"/>
-      <c r="AU108" s="2"/>
-    </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>201</v>
       </c>
@@ -6553,7 +5407,7 @@
         <v>73</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>76</v>
@@ -6570,43 +5424,8 @@
       <c r="L109" s="2">
         <v>134.60525000000001</v>
       </c>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" s="2"/>
-      <c r="Q109" s="2"/>
-      <c r="R109" s="2"/>
-      <c r="S109" s="2"/>
-      <c r="T109" s="2"/>
-      <c r="U109" s="2"/>
-      <c r="V109" s="2"/>
-      <c r="W109" s="2"/>
-      <c r="X109" s="2"/>
-      <c r="Y109" s="2"/>
-      <c r="Z109" s="2"/>
-      <c r="AA109" s="2"/>
-      <c r="AB109" s="2"/>
-      <c r="AC109" s="2"/>
-      <c r="AD109" s="2"/>
-      <c r="AE109" s="2"/>
-      <c r="AF109" s="2"/>
-      <c r="AG109" s="2"/>
-      <c r="AH109" s="2"/>
-      <c r="AI109" s="2"/>
-      <c r="AJ109" s="2"/>
-      <c r="AK109" s="2"/>
-      <c r="AL109" s="2"/>
-      <c r="AM109" s="2"/>
-      <c r="AN109" s="2"/>
-      <c r="AO109" s="2"/>
-      <c r="AP109" s="2"/>
-      <c r="AQ109" s="2"/>
-      <c r="AR109" s="2"/>
-      <c r="AS109" s="2"/>
-      <c r="AT109" s="2"/>
-      <c r="AU109" s="2"/>
-    </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>202</v>
       </c>
@@ -6626,7 +5445,7 @@
         <v>73</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>76</v>
@@ -6643,43 +5462,8 @@
       <c r="L110" s="2">
         <v>134.60525000000001</v>
       </c>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" s="2"/>
-      <c r="Q110" s="2"/>
-      <c r="R110" s="2"/>
-      <c r="S110" s="2"/>
-      <c r="T110" s="2"/>
-      <c r="U110" s="2"/>
-      <c r="V110" s="2"/>
-      <c r="W110" s="2"/>
-      <c r="X110" s="2"/>
-      <c r="Y110" s="2"/>
-      <c r="Z110" s="2"/>
-      <c r="AA110" s="2"/>
-      <c r="AB110" s="2"/>
-      <c r="AC110" s="2"/>
-      <c r="AD110" s="2"/>
-      <c r="AE110" s="2"/>
-      <c r="AF110" s="2"/>
-      <c r="AG110" s="2"/>
-      <c r="AH110" s="2"/>
-      <c r="AI110" s="2"/>
-      <c r="AJ110" s="2"/>
-      <c r="AK110" s="2"/>
-      <c r="AL110" s="2"/>
-      <c r="AM110" s="2"/>
-      <c r="AN110" s="2"/>
-      <c r="AO110" s="2"/>
-      <c r="AP110" s="2"/>
-      <c r="AQ110" s="2"/>
-      <c r="AR110" s="2"/>
-      <c r="AS110" s="2"/>
-      <c r="AT110" s="2"/>
-      <c r="AU110" s="2"/>
-    </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -6705,7 +5489,7 @@
         <v>17</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J111" s="6">
         <v>40967</v>
@@ -6716,43 +5500,8 @@
       <c r="L111" s="2">
         <v>145.96903330000001</v>
       </c>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" s="2"/>
-      <c r="Q111" s="2"/>
-      <c r="R111" s="2"/>
-      <c r="S111" s="2"/>
-      <c r="T111" s="2"/>
-      <c r="U111" s="2"/>
-      <c r="V111" s="2"/>
-      <c r="W111" s="2"/>
-      <c r="X111" s="2"/>
-      <c r="Y111" s="2"/>
-      <c r="Z111" s="2"/>
-      <c r="AA111" s="2"/>
-      <c r="AB111" s="2"/>
-      <c r="AC111" s="2"/>
-      <c r="AD111" s="2"/>
-      <c r="AE111" s="2"/>
-      <c r="AF111" s="2"/>
-      <c r="AG111" s="2"/>
-      <c r="AH111" s="2"/>
-      <c r="AI111" s="2"/>
-      <c r="AJ111" s="2"/>
-      <c r="AK111" s="2"/>
-      <c r="AL111" s="2"/>
-      <c r="AM111" s="2"/>
-      <c r="AN111" s="2"/>
-      <c r="AO111" s="2"/>
-      <c r="AP111" s="2"/>
-      <c r="AQ111" s="2"/>
-      <c r="AR111" s="2"/>
-      <c r="AS111" s="2"/>
-      <c r="AT111" s="2"/>
-      <c r="AU111" s="2"/>
-    </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -6778,7 +5527,7 @@
         <v>17</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J112" s="6">
         <v>40969</v>
@@ -6789,43 +5538,8 @@
       <c r="L112" s="2">
         <v>145.96903330000001</v>
       </c>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" s="2"/>
-      <c r="Q112" s="2"/>
-      <c r="R112" s="2"/>
-      <c r="S112" s="2"/>
-      <c r="T112" s="2"/>
-      <c r="U112" s="2"/>
-      <c r="V112" s="2"/>
-      <c r="W112" s="2"/>
-      <c r="X112" s="2"/>
-      <c r="Y112" s="2"/>
-      <c r="Z112" s="2"/>
-      <c r="AA112" s="2"/>
-      <c r="AB112" s="2"/>
-      <c r="AC112" s="2"/>
-      <c r="AD112" s="2"/>
-      <c r="AE112" s="2"/>
-      <c r="AF112" s="2"/>
-      <c r="AG112" s="2"/>
-      <c r="AH112" s="2"/>
-      <c r="AI112" s="2"/>
-      <c r="AJ112" s="2"/>
-      <c r="AK112" s="2"/>
-      <c r="AL112" s="2"/>
-      <c r="AM112" s="2"/>
-      <c r="AN112" s="2"/>
-      <c r="AO112" s="2"/>
-      <c r="AP112" s="2"/>
-      <c r="AQ112" s="2"/>
-      <c r="AR112" s="2"/>
-      <c r="AS112" s="2"/>
-      <c r="AT112" s="2"/>
-      <c r="AU112" s="2"/>
-    </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>149</v>
       </c>
@@ -6851,7 +5565,7 @@
         <v>17</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J113" s="6">
         <v>40969</v>
@@ -6862,43 +5576,8 @@
       <c r="L113" s="2">
         <v>145.96903330000001</v>
       </c>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" s="2"/>
-      <c r="Q113" s="2"/>
-      <c r="R113" s="2"/>
-      <c r="S113" s="2"/>
-      <c r="T113" s="2"/>
-      <c r="U113" s="2"/>
-      <c r="V113" s="2"/>
-      <c r="W113" s="2"/>
-      <c r="X113" s="2"/>
-      <c r="Y113" s="2"/>
-      <c r="Z113" s="2"/>
-      <c r="AA113" s="2"/>
-      <c r="AB113" s="2"/>
-      <c r="AC113" s="2"/>
-      <c r="AD113" s="2"/>
-      <c r="AE113" s="2"/>
-      <c r="AF113" s="2"/>
-      <c r="AG113" s="2"/>
-      <c r="AH113" s="2"/>
-      <c r="AI113" s="2"/>
-      <c r="AJ113" s="2"/>
-      <c r="AK113" s="2"/>
-      <c r="AL113" s="2"/>
-      <c r="AM113" s="2"/>
-      <c r="AN113" s="2"/>
-      <c r="AO113" s="2"/>
-      <c r="AP113" s="2"/>
-      <c r="AQ113" s="2"/>
-      <c r="AR113" s="2"/>
-      <c r="AS113" s="2"/>
-      <c r="AT113" s="2"/>
-      <c r="AU113" s="2"/>
-    </row>
-    <row r="114" spans="1:47" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>204</v>
       </c>
@@ -6935,43 +5614,8 @@
       <c r="L114" s="2">
         <v>150.10506899999999</v>
       </c>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" s="2"/>
-      <c r="Q114" s="2"/>
-      <c r="R114" s="2"/>
-      <c r="S114" s="2"/>
-      <c r="T114" s="2"/>
-      <c r="U114" s="2"/>
-      <c r="V114" s="2"/>
-      <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
-      <c r="Y114" s="2"/>
-      <c r="Z114" s="2"/>
-      <c r="AA114" s="2"/>
-      <c r="AB114" s="2"/>
-      <c r="AC114" s="2"/>
-      <c r="AD114" s="2"/>
-      <c r="AE114" s="2"/>
-      <c r="AF114" s="2"/>
-      <c r="AG114" s="2"/>
-      <c r="AH114" s="2"/>
-      <c r="AI114" s="2"/>
-      <c r="AJ114" s="2"/>
-      <c r="AK114" s="2"/>
-      <c r="AL114" s="2"/>
-      <c r="AM114" s="2"/>
-      <c r="AN114" s="2"/>
-      <c r="AO114" s="2"/>
-      <c r="AP114" s="2"/>
-      <c r="AQ114" s="2"/>
-      <c r="AR114" s="2"/>
-      <c r="AS114" s="2"/>
-      <c r="AT114" s="2"/>
-      <c r="AU114" s="2"/>
-    </row>
-    <row r="115" spans="1:47" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>205</v>
       </c>
@@ -7008,43 +5652,8 @@
       <c r="L115" s="2">
         <v>150.10506899999999</v>
       </c>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" s="2"/>
-      <c r="Q115" s="2"/>
-      <c r="R115" s="2"/>
-      <c r="S115" s="2"/>
-      <c r="T115" s="2"/>
-      <c r="U115" s="2"/>
-      <c r="V115" s="2"/>
-      <c r="W115" s="2"/>
-      <c r="X115" s="2"/>
-      <c r="Y115" s="2"/>
-      <c r="Z115" s="2"/>
-      <c r="AA115" s="2"/>
-      <c r="AB115" s="2"/>
-      <c r="AC115" s="2"/>
-      <c r="AD115" s="2"/>
-      <c r="AE115" s="2"/>
-      <c r="AF115" s="2"/>
-      <c r="AG115" s="2"/>
-      <c r="AH115" s="2"/>
-      <c r="AI115" s="2"/>
-      <c r="AJ115" s="2"/>
-      <c r="AK115" s="2"/>
-      <c r="AL115" s="2"/>
-      <c r="AM115" s="2"/>
-      <c r="AN115" s="2"/>
-      <c r="AO115" s="2"/>
-      <c r="AP115" s="2"/>
-      <c r="AQ115" s="2"/>
-      <c r="AR115" s="2"/>
-      <c r="AS115" s="2"/>
-      <c r="AT115" s="2"/>
-      <c r="AU115" s="2"/>
-    </row>
-    <row r="116" spans="1:47" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>206</v>
       </c>
@@ -7081,43 +5690,8 @@
       <c r="L116" s="2">
         <v>150.10506899999999</v>
       </c>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2"/>
-      <c r="Q116" s="2"/>
-      <c r="R116" s="2"/>
-      <c r="S116" s="2"/>
-      <c r="T116" s="2"/>
-      <c r="U116" s="2"/>
-      <c r="V116" s="2"/>
-      <c r="W116" s="2"/>
-      <c r="X116" s="2"/>
-      <c r="Y116" s="2"/>
-      <c r="Z116" s="2"/>
-      <c r="AA116" s="2"/>
-      <c r="AB116" s="2"/>
-      <c r="AC116" s="2"/>
-      <c r="AD116" s="2"/>
-      <c r="AE116" s="2"/>
-      <c r="AF116" s="2"/>
-      <c r="AG116" s="2"/>
-      <c r="AH116" s="2"/>
-      <c r="AI116" s="2"/>
-      <c r="AJ116" s="2"/>
-      <c r="AK116" s="2"/>
-      <c r="AL116" s="2"/>
-      <c r="AM116" s="2"/>
-      <c r="AN116" s="2"/>
-      <c r="AO116" s="2"/>
-      <c r="AP116" s="2"/>
-      <c r="AQ116" s="2"/>
-      <c r="AR116" s="2"/>
-      <c r="AS116" s="2"/>
-      <c r="AT116" s="2"/>
-      <c r="AU116" s="2"/>
-    </row>
-    <row r="117" spans="1:47" ht="18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>207</v>
       </c>
@@ -7154,43 +5728,8 @@
       <c r="L117" s="2">
         <v>150.10506899999999</v>
       </c>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" s="2"/>
-      <c r="Q117" s="2"/>
-      <c r="R117" s="2"/>
-      <c r="S117" s="2"/>
-      <c r="T117" s="2"/>
-      <c r="U117" s="2"/>
-      <c r="V117" s="2"/>
-      <c r="W117" s="2"/>
-      <c r="X117" s="2"/>
-      <c r="Y117" s="2"/>
-      <c r="Z117" s="2"/>
-      <c r="AA117" s="2"/>
-      <c r="AB117" s="2"/>
-      <c r="AC117" s="2"/>
-      <c r="AD117" s="2"/>
-      <c r="AE117" s="2"/>
-      <c r="AF117" s="2"/>
-      <c r="AG117" s="2"/>
-      <c r="AH117" s="2"/>
-      <c r="AI117" s="2"/>
-      <c r="AJ117" s="2"/>
-      <c r="AK117" s="2"/>
-      <c r="AL117" s="2"/>
-      <c r="AM117" s="2"/>
-      <c r="AN117" s="2"/>
-      <c r="AO117" s="2"/>
-      <c r="AP117" s="2"/>
-      <c r="AQ117" s="2"/>
-      <c r="AR117" s="2"/>
-      <c r="AS117" s="2"/>
-      <c r="AT117" s="2"/>
-      <c r="AU117" s="2"/>
-    </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>150</v>
       </c>
@@ -7216,7 +5755,7 @@
         <v>10</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J118" s="6">
         <v>39050</v>
@@ -7227,43 +5766,8 @@
       <c r="L118" s="2">
         <v>161.8881667</v>
       </c>
-      <c r="M118" s="2"/>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" s="2"/>
-      <c r="Q118" s="2"/>
-      <c r="R118" s="2"/>
-      <c r="S118" s="2"/>
-      <c r="T118" s="2"/>
-      <c r="U118" s="2"/>
-      <c r="V118" s="2"/>
-      <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
-      <c r="Y118" s="2"/>
-      <c r="Z118" s="2"/>
-      <c r="AA118" s="2"/>
-      <c r="AB118" s="2"/>
-      <c r="AC118" s="2"/>
-      <c r="AD118" s="2"/>
-      <c r="AE118" s="2"/>
-      <c r="AF118" s="2"/>
-      <c r="AG118" s="2"/>
-      <c r="AH118" s="2"/>
-      <c r="AI118" s="2"/>
-      <c r="AJ118" s="2"/>
-      <c r="AK118" s="2"/>
-      <c r="AL118" s="2"/>
-      <c r="AM118" s="2"/>
-      <c r="AN118" s="2"/>
-      <c r="AO118" s="2"/>
-      <c r="AP118" s="2"/>
-      <c r="AQ118" s="2"/>
-      <c r="AR118" s="2"/>
-      <c r="AS118" s="2"/>
-      <c r="AT118" s="2"/>
-      <c r="AU118" s="2"/>
-    </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>151</v>
       </c>
@@ -7289,7 +5793,7 @@
         <v>10</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J119" s="6">
         <v>39054</v>
@@ -7300,43 +5804,8 @@
       <c r="L119" s="2">
         <v>161.8881667</v>
       </c>
-      <c r="M119" s="2"/>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" s="2"/>
-      <c r="Q119" s="2"/>
-      <c r="R119" s="2"/>
-      <c r="S119" s="2"/>
-      <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
-      <c r="V119" s="2"/>
-      <c r="W119" s="2"/>
-      <c r="X119" s="2"/>
-      <c r="Y119" s="2"/>
-      <c r="Z119" s="2"/>
-      <c r="AA119" s="2"/>
-      <c r="AB119" s="2"/>
-      <c r="AC119" s="2"/>
-      <c r="AD119" s="2"/>
-      <c r="AE119" s="2"/>
-      <c r="AF119" s="2"/>
-      <c r="AG119" s="2"/>
-      <c r="AH119" s="2"/>
-      <c r="AI119" s="2"/>
-      <c r="AJ119" s="2"/>
-      <c r="AK119" s="2"/>
-      <c r="AL119" s="2"/>
-      <c r="AM119" s="2"/>
-      <c r="AN119" s="2"/>
-      <c r="AO119" s="2"/>
-      <c r="AP119" s="2"/>
-      <c r="AQ119" s="2"/>
-      <c r="AR119" s="2"/>
-      <c r="AS119" s="2"/>
-      <c r="AT119" s="2"/>
-      <c r="AU119" s="2"/>
-    </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>152</v>
       </c>
@@ -7362,7 +5831,7 @@
         <v>10</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J120" s="6">
         <v>43284</v>
@@ -7373,43 +5842,8 @@
       <c r="L120" s="2">
         <v>161.899</v>
       </c>
-      <c r="M120" s="2"/>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" s="2"/>
-      <c r="Q120" s="2"/>
-      <c r="R120" s="2"/>
-      <c r="S120" s="2"/>
-      <c r="T120" s="2"/>
-      <c r="U120" s="2"/>
-      <c r="V120" s="2"/>
-      <c r="W120" s="2"/>
-      <c r="X120" s="2"/>
-      <c r="Y120" s="2"/>
-      <c r="Z120" s="2"/>
-      <c r="AA120" s="2"/>
-      <c r="AB120" s="2"/>
-      <c r="AC120" s="2"/>
-      <c r="AD120" s="2"/>
-      <c r="AE120" s="2"/>
-      <c r="AF120" s="2"/>
-      <c r="AG120" s="2"/>
-      <c r="AH120" s="2"/>
-      <c r="AI120" s="2"/>
-      <c r="AJ120" s="2"/>
-      <c r="AK120" s="2"/>
-      <c r="AL120" s="2"/>
-      <c r="AM120" s="2"/>
-      <c r="AN120" s="2"/>
-      <c r="AO120" s="2"/>
-      <c r="AP120" s="2"/>
-      <c r="AQ120" s="2"/>
-      <c r="AR120" s="2"/>
-      <c r="AS120" s="2"/>
-      <c r="AT120" s="2"/>
-      <c r="AU120" s="2"/>
-    </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>153</v>
       </c>
@@ -7435,7 +5869,7 @@
         <v>10</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J121" s="6">
         <v>43285</v>
@@ -7446,43 +5880,8 @@
       <c r="L121" s="2">
         <v>161.899</v>
       </c>
-      <c r="M121" s="2"/>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" s="2"/>
-      <c r="Q121" s="2"/>
-      <c r="R121" s="2"/>
-      <c r="S121" s="2"/>
-      <c r="T121" s="2"/>
-      <c r="U121" s="2"/>
-      <c r="V121" s="2"/>
-      <c r="W121" s="2"/>
-      <c r="X121" s="2"/>
-      <c r="Y121" s="2"/>
-      <c r="Z121" s="2"/>
-      <c r="AA121" s="2"/>
-      <c r="AB121" s="2"/>
-      <c r="AC121" s="2"/>
-      <c r="AD121" s="2"/>
-      <c r="AE121" s="2"/>
-      <c r="AF121" s="2"/>
-      <c r="AG121" s="2"/>
-      <c r="AH121" s="2"/>
-      <c r="AI121" s="2"/>
-      <c r="AJ121" s="2"/>
-      <c r="AK121" s="2"/>
-      <c r="AL121" s="2"/>
-      <c r="AM121" s="2"/>
-      <c r="AN121" s="2"/>
-      <c r="AO121" s="2"/>
-      <c r="AP121" s="2"/>
-      <c r="AQ121" s="2"/>
-      <c r="AR121" s="2"/>
-      <c r="AS121" s="2"/>
-      <c r="AT121" s="2"/>
-      <c r="AU121" s="2"/>
-    </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>154</v>
       </c>
@@ -7508,7 +5907,7 @@
         <v>10</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J122" s="6">
         <v>43291</v>
@@ -7519,43 +5918,8 @@
       <c r="L122" s="2">
         <v>161.93199999999999</v>
       </c>
-      <c r="M122" s="2"/>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" s="2"/>
-      <c r="Q122" s="2"/>
-      <c r="R122" s="2"/>
-      <c r="S122" s="2"/>
-      <c r="T122" s="2"/>
-      <c r="U122" s="2"/>
-      <c r="V122" s="2"/>
-      <c r="W122" s="2"/>
-      <c r="X122" s="2"/>
-      <c r="Y122" s="2"/>
-      <c r="Z122" s="2"/>
-      <c r="AA122" s="2"/>
-      <c r="AB122" s="2"/>
-      <c r="AC122" s="2"/>
-      <c r="AD122" s="2"/>
-      <c r="AE122" s="2"/>
-      <c r="AF122" s="2"/>
-      <c r="AG122" s="2"/>
-      <c r="AH122" s="2"/>
-      <c r="AI122" s="2"/>
-      <c r="AJ122" s="2"/>
-      <c r="AK122" s="2"/>
-      <c r="AL122" s="2"/>
-      <c r="AM122" s="2"/>
-      <c r="AN122" s="2"/>
-      <c r="AO122" s="2"/>
-      <c r="AP122" s="2"/>
-      <c r="AQ122" s="2"/>
-      <c r="AR122" s="2"/>
-      <c r="AS122" s="2"/>
-      <c r="AT122" s="2"/>
-      <c r="AU122" s="2"/>
-    </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>155</v>
       </c>
@@ -7581,7 +5945,7 @@
         <v>10</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J123" s="6">
         <v>43292</v>
@@ -7592,43 +5956,8 @@
       <c r="L123" s="2">
         <v>161.93199999999999</v>
       </c>
-      <c r="M123" s="2"/>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" s="2"/>
-      <c r="Q123" s="2"/>
-      <c r="R123" s="2"/>
-      <c r="S123" s="2"/>
-      <c r="T123" s="2"/>
-      <c r="U123" s="2"/>
-      <c r="V123" s="2"/>
-      <c r="W123" s="2"/>
-      <c r="X123" s="2"/>
-      <c r="Y123" s="2"/>
-      <c r="Z123" s="2"/>
-      <c r="AA123" s="2"/>
-      <c r="AB123" s="2"/>
-      <c r="AC123" s="2"/>
-      <c r="AD123" s="2"/>
-      <c r="AE123" s="2"/>
-      <c r="AF123" s="2"/>
-      <c r="AG123" s="2"/>
-      <c r="AH123" s="2"/>
-      <c r="AI123" s="2"/>
-      <c r="AJ123" s="2"/>
-      <c r="AK123" s="2"/>
-      <c r="AL123" s="2"/>
-      <c r="AM123" s="2"/>
-      <c r="AN123" s="2"/>
-      <c r="AO123" s="2"/>
-      <c r="AP123" s="2"/>
-      <c r="AQ123" s="2"/>
-      <c r="AR123" s="2"/>
-      <c r="AS123" s="2"/>
-      <c r="AT123" s="2"/>
-      <c r="AU123" s="2"/>
-    </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>209</v>
       </c>
@@ -7651,7 +5980,7 @@
         <v>38</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J124" s="3" t="s">
         <v>221</v>
@@ -7662,43 +5991,8 @@
       <c r="L124" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M124" s="2"/>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" s="2"/>
-      <c r="Q124" s="2"/>
-      <c r="R124" s="2"/>
-      <c r="S124" s="2"/>
-      <c r="T124" s="2"/>
-      <c r="U124" s="2"/>
-      <c r="V124" s="2"/>
-      <c r="W124" s="2"/>
-      <c r="X124" s="2"/>
-      <c r="Y124" s="2"/>
-      <c r="Z124" s="2"/>
-      <c r="AA124" s="2"/>
-      <c r="AB124" s="2"/>
-      <c r="AC124" s="2"/>
-      <c r="AD124" s="2"/>
-      <c r="AE124" s="2"/>
-      <c r="AF124" s="2"/>
-      <c r="AG124" s="2"/>
-      <c r="AH124" s="2"/>
-      <c r="AI124" s="2"/>
-      <c r="AJ124" s="2"/>
-      <c r="AK124" s="2"/>
-      <c r="AL124" s="2"/>
-      <c r="AM124" s="2"/>
-      <c r="AN124" s="2"/>
-      <c r="AO124" s="2"/>
-      <c r="AP124" s="2"/>
-      <c r="AQ124" s="2"/>
-      <c r="AR124" s="2"/>
-      <c r="AS124" s="2"/>
-      <c r="AT124" s="2"/>
-      <c r="AU124" s="2"/>
-    </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>210</v>
       </c>
@@ -7721,7 +6015,7 @@
         <v>38</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>221</v>
@@ -7732,43 +6026,8 @@
       <c r="L125" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M125" s="2"/>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" s="2"/>
-      <c r="Q125" s="2"/>
-      <c r="R125" s="2"/>
-      <c r="S125" s="2"/>
-      <c r="T125" s="2"/>
-      <c r="U125" s="2"/>
-      <c r="V125" s="2"/>
-      <c r="W125" s="2"/>
-      <c r="X125" s="2"/>
-      <c r="Y125" s="2"/>
-      <c r="Z125" s="2"/>
-      <c r="AA125" s="2"/>
-      <c r="AB125" s="2"/>
-      <c r="AC125" s="2"/>
-      <c r="AD125" s="2"/>
-      <c r="AE125" s="2"/>
-      <c r="AF125" s="2"/>
-      <c r="AG125" s="2"/>
-      <c r="AH125" s="2"/>
-      <c r="AI125" s="2"/>
-      <c r="AJ125" s="2"/>
-      <c r="AK125" s="2"/>
-      <c r="AL125" s="2"/>
-      <c r="AM125" s="2"/>
-      <c r="AN125" s="2"/>
-      <c r="AO125" s="2"/>
-      <c r="AP125" s="2"/>
-      <c r="AQ125" s="2"/>
-      <c r="AR125" s="2"/>
-      <c r="AS125" s="2"/>
-      <c r="AT125" s="2"/>
-      <c r="AU125" s="2"/>
-    </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>211</v>
       </c>
@@ -7791,7 +6050,7 @@
         <v>38</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J126" s="3" t="s">
         <v>221</v>
@@ -7802,43 +6061,8 @@
       <c r="L126" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M126" s="2"/>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" s="2"/>
-      <c r="Q126" s="2"/>
-      <c r="R126" s="2"/>
-      <c r="S126" s="2"/>
-      <c r="T126" s="2"/>
-      <c r="U126" s="2"/>
-      <c r="V126" s="2"/>
-      <c r="W126" s="2"/>
-      <c r="X126" s="2"/>
-      <c r="Y126" s="2"/>
-      <c r="Z126" s="2"/>
-      <c r="AA126" s="2"/>
-      <c r="AB126" s="2"/>
-      <c r="AC126" s="2"/>
-      <c r="AD126" s="2"/>
-      <c r="AE126" s="2"/>
-      <c r="AF126" s="2"/>
-      <c r="AG126" s="2"/>
-      <c r="AH126" s="2"/>
-      <c r="AI126" s="2"/>
-      <c r="AJ126" s="2"/>
-      <c r="AK126" s="2"/>
-      <c r="AL126" s="2"/>
-      <c r="AM126" s="2"/>
-      <c r="AN126" s="2"/>
-      <c r="AO126" s="2"/>
-      <c r="AP126" s="2"/>
-      <c r="AQ126" s="2"/>
-      <c r="AR126" s="2"/>
-      <c r="AS126" s="2"/>
-      <c r="AT126" s="2"/>
-      <c r="AU126" s="2"/>
-    </row>
-    <row r="127" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>212</v>
       </c>
@@ -7861,7 +6085,7 @@
         <v>38</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>221</v>
@@ -7872,43 +6096,8 @@
       <c r="L127" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M127" s="2"/>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" s="2"/>
-      <c r="Q127" s="2"/>
-      <c r="R127" s="2"/>
-      <c r="S127" s="2"/>
-      <c r="T127" s="2"/>
-      <c r="U127" s="2"/>
-      <c r="V127" s="2"/>
-      <c r="W127" s="2"/>
-      <c r="X127" s="2"/>
-      <c r="Y127" s="2"/>
-      <c r="Z127" s="2"/>
-      <c r="AA127" s="2"/>
-      <c r="AB127" s="2"/>
-      <c r="AC127" s="2"/>
-      <c r="AD127" s="2"/>
-      <c r="AE127" s="2"/>
-      <c r="AF127" s="2"/>
-      <c r="AG127" s="2"/>
-      <c r="AH127" s="2"/>
-      <c r="AI127" s="2"/>
-      <c r="AJ127" s="2"/>
-      <c r="AK127" s="2"/>
-      <c r="AL127" s="2"/>
-      <c r="AM127" s="2"/>
-      <c r="AN127" s="2"/>
-      <c r="AO127" s="2"/>
-      <c r="AP127" s="2"/>
-      <c r="AQ127" s="2"/>
-      <c r="AR127" s="2"/>
-      <c r="AS127" s="2"/>
-      <c r="AT127" s="2"/>
-      <c r="AU127" s="2"/>
-    </row>
-    <row r="128" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>213</v>
       </c>
@@ -7931,7 +6120,7 @@
         <v>38</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J128" s="3" t="s">
         <v>221</v>
@@ -7942,43 +6131,8 @@
       <c r="L128" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" s="2"/>
-      <c r="Q128" s="2"/>
-      <c r="R128" s="2"/>
-      <c r="S128" s="2"/>
-      <c r="T128" s="2"/>
-      <c r="U128" s="2"/>
-      <c r="V128" s="2"/>
-      <c r="W128" s="2"/>
-      <c r="X128" s="2"/>
-      <c r="Y128" s="2"/>
-      <c r="Z128" s="2"/>
-      <c r="AA128" s="2"/>
-      <c r="AB128" s="2"/>
-      <c r="AC128" s="2"/>
-      <c r="AD128" s="2"/>
-      <c r="AE128" s="2"/>
-      <c r="AF128" s="2"/>
-      <c r="AG128" s="2"/>
-      <c r="AH128" s="2"/>
-      <c r="AI128" s="2"/>
-      <c r="AJ128" s="2"/>
-      <c r="AK128" s="2"/>
-      <c r="AL128" s="2"/>
-      <c r="AM128" s="2"/>
-      <c r="AN128" s="2"/>
-      <c r="AO128" s="2"/>
-      <c r="AP128" s="2"/>
-      <c r="AQ128" s="2"/>
-      <c r="AR128" s="2"/>
-      <c r="AS128" s="2"/>
-      <c r="AT128" s="2"/>
-      <c r="AU128" s="2"/>
-    </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>214</v>
       </c>
@@ -8001,7 +6155,7 @@
         <v>38</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>221</v>
@@ -8012,43 +6166,8 @@
       <c r="L129" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" s="2"/>
-      <c r="Q129" s="2"/>
-      <c r="R129" s="2"/>
-      <c r="S129" s="2"/>
-      <c r="T129" s="2"/>
-      <c r="U129" s="2"/>
-      <c r="V129" s="2"/>
-      <c r="W129" s="2"/>
-      <c r="X129" s="2"/>
-      <c r="Y129" s="2"/>
-      <c r="Z129" s="2"/>
-      <c r="AA129" s="2"/>
-      <c r="AB129" s="2"/>
-      <c r="AC129" s="2"/>
-      <c r="AD129" s="2"/>
-      <c r="AE129" s="2"/>
-      <c r="AF129" s="2"/>
-      <c r="AG129" s="2"/>
-      <c r="AH129" s="2"/>
-      <c r="AI129" s="2"/>
-      <c r="AJ129" s="2"/>
-      <c r="AK129" s="2"/>
-      <c r="AL129" s="2"/>
-      <c r="AM129" s="2"/>
-      <c r="AN129" s="2"/>
-      <c r="AO129" s="2"/>
-      <c r="AP129" s="2"/>
-      <c r="AQ129" s="2"/>
-      <c r="AR129" s="2"/>
-      <c r="AS129" s="2"/>
-      <c r="AT129" s="2"/>
-      <c r="AU129" s="2"/>
-    </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>215</v>
       </c>
@@ -8071,7 +6190,7 @@
         <v>38</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J130" s="3" t="s">
         <v>221</v>
@@ -8082,43 +6201,8 @@
       <c r="L130" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M130" s="2"/>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" s="2"/>
-      <c r="Q130" s="2"/>
-      <c r="R130" s="2"/>
-      <c r="S130" s="2"/>
-      <c r="T130" s="2"/>
-      <c r="U130" s="2"/>
-      <c r="V130" s="2"/>
-      <c r="W130" s="2"/>
-      <c r="X130" s="2"/>
-      <c r="Y130" s="2"/>
-      <c r="Z130" s="2"/>
-      <c r="AA130" s="2"/>
-      <c r="AB130" s="2"/>
-      <c r="AC130" s="2"/>
-      <c r="AD130" s="2"/>
-      <c r="AE130" s="2"/>
-      <c r="AF130" s="2"/>
-      <c r="AG130" s="2"/>
-      <c r="AH130" s="2"/>
-      <c r="AI130" s="2"/>
-      <c r="AJ130" s="2"/>
-      <c r="AK130" s="2"/>
-      <c r="AL130" s="2"/>
-      <c r="AM130" s="2"/>
-      <c r="AN130" s="2"/>
-      <c r="AO130" s="2"/>
-      <c r="AP130" s="2"/>
-      <c r="AQ130" s="2"/>
-      <c r="AR130" s="2"/>
-      <c r="AS130" s="2"/>
-      <c r="AT130" s="2"/>
-      <c r="AU130" s="2"/>
-    </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>208</v>
       </c>
@@ -8144,7 +6228,7 @@
         <v>38</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J131" s="6">
         <v>39418</v>
@@ -8155,43 +6239,8 @@
       <c r="L131" s="2">
         <v>161.94300000000001</v>
       </c>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2"/>
-      <c r="Q131" s="2"/>
-      <c r="R131" s="2"/>
-      <c r="S131" s="2"/>
-      <c r="T131" s="2"/>
-      <c r="U131" s="2"/>
-      <c r="V131" s="2"/>
-      <c r="W131" s="2"/>
-      <c r="X131" s="2"/>
-      <c r="Y131" s="2"/>
-      <c r="Z131" s="2"/>
-      <c r="AA131" s="2"/>
-      <c r="AB131" s="2"/>
-      <c r="AC131" s="2"/>
-      <c r="AD131" s="2"/>
-      <c r="AE131" s="2"/>
-      <c r="AF131" s="2"/>
-      <c r="AG131" s="2"/>
-      <c r="AH131" s="2"/>
-      <c r="AI131" s="2"/>
-      <c r="AJ131" s="2"/>
-      <c r="AK131" s="2"/>
-      <c r="AL131" s="2"/>
-      <c r="AM131" s="2"/>
-      <c r="AN131" s="2"/>
-      <c r="AO131" s="2"/>
-      <c r="AP131" s="2"/>
-      <c r="AQ131" s="2"/>
-      <c r="AR131" s="2"/>
-      <c r="AS131" s="2"/>
-      <c r="AT131" s="2"/>
-      <c r="AU131" s="2"/>
-    </row>
-    <row r="132" spans="1:47" ht="20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>179</v>
       </c>
@@ -8208,16 +6257,16 @@
         <v>8</v>
       </c>
       <c r="F132" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I132" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J132" s="8">
         <v>39997</v>
@@ -8228,11 +6277,8 @@
       <c r="L132" s="9">
         <v>136.54400000000001</v>
       </c>
-      <c r="M132" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="133" spans="1:47" ht="20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>180</v>
       </c>
@@ -8249,16 +6295,16 @@
         <v>8</v>
       </c>
       <c r="F133" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G133" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I133" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J133" s="8">
         <v>39997</v>
@@ -8269,11 +6315,8 @@
       <c r="L133" s="9">
         <v>136.54400000000001</v>
       </c>
-      <c r="M133" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="134" spans="1:47" ht="20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>181</v>
       </c>
@@ -8287,16 +6330,16 @@
         <v>8</v>
       </c>
       <c r="F134" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H134" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I134" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J134" s="8">
         <v>39998</v>
@@ -8307,11 +6350,8 @@
       <c r="L134" s="9">
         <v>136.619</v>
       </c>
-      <c r="M134" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="135" spans="1:47" ht="20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:12" ht="20" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>182</v>
       </c>
@@ -8325,16 +6365,16 @@
         <v>8</v>
       </c>
       <c r="F135" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I135" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J135" s="8">
         <v>40003</v>
@@ -8345,11 +6385,8 @@
       <c r="L135" s="9">
         <v>135.31899999999999</v>
       </c>
-      <c r="M135" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="136" spans="1:47" ht="29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:12" ht="29" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>183</v>
       </c>
@@ -8363,16 +6400,16 @@
         <v>8</v>
       </c>
       <c r="F136" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H136" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G136" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I136" s="10" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J136" s="8">
         <v>40005</v>
@@ -8382,9 +6419,6 @@
       </c>
       <c r="L136" s="9">
         <v>135.28399999999999</v>
-      </c>
-      <c r="M136" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
